--- a/artfynd/A 6671-2026 artfynd.xlsx
+++ b/artfynd/A 6671-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124676361</v>
+        <v>124677257</v>
       </c>
       <c r="B2" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mockflån, Dlr</t>
+          <t>Flatån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468888</v>
+        <v>468958</v>
       </c>
       <c r="R2" t="n">
-        <v>6720089</v>
+        <v>6719606</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124675692</v>
+        <v>124676068</v>
       </c>
       <c r="B3" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468763</v>
+        <v>468992</v>
       </c>
       <c r="R3" t="n">
-        <v>6720271</v>
+        <v>6720213</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124676176</v>
+        <v>124675584</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468937</v>
+        <v>468676</v>
       </c>
       <c r="R4" t="n">
-        <v>6720185</v>
+        <v>6720276</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124676284</v>
+        <v>124675910</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468888</v>
+        <v>468846</v>
       </c>
       <c r="R5" t="n">
-        <v>6720107</v>
+        <v>6720277</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124676158</v>
+        <v>124675931</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468955</v>
+        <v>468843</v>
       </c>
       <c r="R6" t="n">
-        <v>6720166</v>
+        <v>6720296</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,19 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124676306</v>
+        <v>124676078</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1248,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468875</v>
+        <v>468981</v>
       </c>
       <c r="R7" t="n">
-        <v>6720097</v>
+        <v>6720215</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1311,19 +1281,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124676078</v>
+        <v>124676158</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1354,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468981</v>
+        <v>468955</v>
       </c>
       <c r="R8" t="n">
-        <v>6720215</v>
+        <v>6720166</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1417,48 +1382,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124676034</v>
+        <v>124676176</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1466,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468971</v>
+        <v>468937</v>
       </c>
       <c r="R9" t="n">
-        <v>6720349</v>
+        <v>6720185</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1529,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124675609</v>
+        <v>124676187</v>
       </c>
       <c r="B10" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468705</v>
+        <v>468941</v>
       </c>
       <c r="R10" t="n">
-        <v>6720281</v>
+        <v>6720166</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1635,19 +1584,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124676342</v>
+        <v>124676284</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1678,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468876</v>
+        <v>468888</v>
       </c>
       <c r="R11" t="n">
-        <v>6720083</v>
+        <v>6720107</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1741,47 +1685,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124675989</v>
+        <v>124676291</v>
       </c>
       <c r="B12" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1789,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468871</v>
+        <v>468873</v>
       </c>
       <c r="R12" t="n">
-        <v>6720345</v>
+        <v>6720117</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1833,6 +1767,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1851,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124676897</v>
+        <v>124676306</v>
       </c>
       <c r="B13" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468935</v>
+        <v>468875</v>
       </c>
       <c r="R13" t="n">
-        <v>6720026</v>
+        <v>6720097</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1957,19 +1887,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124675910</v>
+        <v>124676323</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2000,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468846</v>
+        <v>468891</v>
       </c>
       <c r="R14" t="n">
-        <v>6720277</v>
+        <v>6720084</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2063,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124676387</v>
+        <v>124676342</v>
       </c>
       <c r="B15" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468884</v>
+        <v>468876</v>
       </c>
       <c r="R15" t="n">
-        <v>6720070</v>
+        <v>6720083</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2169,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124675677</v>
+        <v>124676558</v>
       </c>
       <c r="B16" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468773</v>
+        <v>468865</v>
       </c>
       <c r="R16" t="n">
-        <v>6720277</v>
+        <v>6720060</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2275,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124676405</v>
+        <v>124675609</v>
       </c>
       <c r="B17" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>468705</v>
       </c>
       <c r="R17" t="n">
-        <v>6720092</v>
+        <v>6720281</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2381,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124676068</v>
+        <v>124676113</v>
       </c>
       <c r="B18" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468992</v>
+        <v>468948</v>
       </c>
       <c r="R18" t="n">
-        <v>6720213</v>
+        <v>6720182</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2487,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124676113</v>
+        <v>124676139</v>
       </c>
       <c r="B19" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,10 +2430,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468948</v>
+        <v>468939</v>
       </c>
       <c r="R19" t="n">
-        <v>6720182</v>
+        <v>6720175</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2593,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124676291</v>
+        <v>124676405</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2531,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468873</v>
+        <v>468874</v>
       </c>
       <c r="R20" t="n">
-        <v>6720117</v>
+        <v>6720092</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2699,42 +2594,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124676323</v>
+        <v>124675989</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2742,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468891</v>
+        <v>468871</v>
       </c>
       <c r="R21" t="n">
-        <v>6720084</v>
+        <v>6720345</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2786,7 +2681,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,42 +2699,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124676139</v>
+        <v>124676034</v>
       </c>
       <c r="B22" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2848,10 +2743,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468939</v>
+        <v>468971</v>
       </c>
       <c r="R22" t="n">
-        <v>6720175</v>
+        <v>6720349</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2911,15 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124675931</v>
+        <v>124675677</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,21 +2817,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2954,10 +2844,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468843</v>
+        <v>468773</v>
       </c>
       <c r="R23" t="n">
-        <v>6720296</v>
+        <v>6720277</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3017,15 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124676187</v>
+        <v>124675692</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +2918,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3060,10 +2945,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468941</v>
+        <v>468763</v>
       </c>
       <c r="R24" t="n">
-        <v>6720166</v>
+        <v>6720271</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3123,15 +3008,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124675584</v>
+        <v>124676361</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3019,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3046,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468676</v>
+        <v>468888</v>
       </c>
       <c r="R25" t="n">
-        <v>6720276</v>
+        <v>6720089</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3229,15 +3109,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124676558</v>
+        <v>124676375</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,21 +3120,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3272,10 +3147,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468865</v>
+        <v>468867</v>
       </c>
       <c r="R26" t="n">
-        <v>6720060</v>
+        <v>6720092</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3335,15 +3210,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124676375</v>
+        <v>124676387</v>
       </c>
       <c r="B27" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468867</v>
+        <v>468884</v>
       </c>
       <c r="R27" t="n">
-        <v>6720092</v>
+        <v>6720070</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3441,15 +3311,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124677257</v>
+        <v>124676897</v>
       </c>
       <c r="B28" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,14 +3345,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flatån, Dlr</t>
+          <t>Mockflån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468958</v>
+        <v>468935</v>
       </c>
       <c r="R28" t="n">
-        <v>6719606</v>
+        <v>6720026</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>

--- a/artfynd/A 6671-2026 artfynd.xlsx
+++ b/artfynd/A 6671-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676068</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675584</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675931</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676078</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676176</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676187</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676284</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676291</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676306</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676323</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676342</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676558</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675609</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676113</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676139</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676405</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675989</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676034</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675677</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2904,6 +3014,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675692</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3005,6 +3120,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676361</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3106,6 +3226,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676375</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3207,6 +3332,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676387</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3308,6 +3438,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124676897</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3409,8 +3544,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124677257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>